--- a/data/leads/obuchenie_personala.xlsx
+++ b/data/leads/obuchenie_personala.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Обучение персонала" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обучение персонала'!$A$1:$N$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Обучение персонала'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,8 @@
     <col width="52" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -517,6 +518,11 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Проверка</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Фрагмент, где найдено</t>
         </is>
       </c>
@@ -547,11 +553,7 @@
           <t>https://surgutneftegas.ru</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>отдела кадров</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>начальник отдела кадров</t>
@@ -563,7 +565,11 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>+7 (346) 243-27-88</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>https://www.surpk.ru/social-partnership/vacancy-view?id=62</t>
@@ -579,7 +585,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Сургутское управление буровых работ №3 ПАО «Сургутнефтегаз» приглашает для ... Андреева Елена Александровна, начальник отдела кадров - (3462) 43-27-88;. ПАО "Сургутнефтегаз" Сургутское УБР №3</t>
         </is>
@@ -643,7 +654,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>... ПАО «Сургутнефтегаз». Контактные лица для справок - Бачурин Александр Вячеславович, начальник отдела кадров Управления поисково-разведочных... Сургутнефтегаз</t>
         </is>
@@ -707,7 +723,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>Контактные данные отделов кадров структурных подразделений ПАО «Сургутнефтегаз» для трудоустройства: ; +7(346) 241-06-82 · out.hr-18@surgutneftegas.ru ; +7(346)... Контакты всех отделов кадров «Сургутнефтегаза</t>
         </is>
@@ -739,22 +760,22 @@
           <t>https://surgutneftegas.ru</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Учебного Центр</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Начальник отдела кадров</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Бакунов А. С.</t>
+          <t>Гатиатуллина Рушания Тагировна</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://sibadi.org/news/sotrudnichestvo_sibadi_s_sugrutneftegaz/</t>
+          <t>https://www.surpk.ru/social-partnership/vacancy-view?id=117</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -767,9 +788,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>и директор Федерального Учебного Центра Бакунов А.С. СМТ-2 ПАО «Сургутнефтегаз» было представлено руководителями: Синявский Владимир... Сотрудничество с ключевым партнёром</t>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>Начальник отдела кадров Гатиатуллина Рушания Тагировна;. Заместитель ... ПАО «СУРГУТНЕФТЕГАЗ» Сургутское управление буровых работ № 3 · Вакансия. ПАО... НГДУ «Нижнесортымскнефть</t>
         </is>
       </c>
     </row>
@@ -801,20 +827,20 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>отдел кадров</t>
+          <t>Учебного Центр</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Бакунов А. С.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>+7 (346) 241-49-08</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://surpk.ru/social-partnership/vacancy-view?id=80</t>
+          <t>https://sibadi.org/news/sotrudnichestvo_sibadi_s_sugrutneftegaz/</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -827,54 +853,59 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО «Сургутнефтегаз» · По всем интересующим Вас вопросам можно обратиться по телефону: · 8 (3462) 41-49-08 (отдел кадров). ПАО "Сургутнефтегаз" УВСИНГ</t>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>и директор Федерального Учебного Центра Бакунов А.С. СМТ-2 ПАО «Сургутнефтегаз» было представлено руководителями: Синявский Владимир... Сотрудничество с ключевым партнёром</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ПАО "СУРГУТНЕФТЕГАЗ"</t>
+          <t>ПАО "ГАЗ"</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8602060555</t>
+          <t>5200000046</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>860201001</t>
+          <t>525601001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ - Югра</t>
+          <t>Нижегородская область</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://surgutneftegas.ru</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Учебный центр</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+          <t>https://gaz.ru</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Заместитель генерального директора по управлению персоналом</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Недоборенко Лилия Викторовна</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>+7 (495) 357-25-75</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.michko.ru/ru/our-project/facade/uchebny-centr-cpto</t>
+          <t>https://www.rostovoblgaz.ru/company/management/</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -884,114 +915,153 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Учебный центр ЦПТО ОАО "Сургутнефтегаз" - ЛБК Мичко. Тел: +7(495) 357 2575 ... Контакты. Copyright 2017 © LBK Michko. Учебный центр ЦПТО ОАО "Сургутнефтегаз"</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Недоборенко Лилия Викторовна. Заместитель генерального директора по управлению персоналом и общим вопросам ... Хочешь газ? Подай заявку! Подробнее ›. Руководство - ПАО</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ПАО "СУРГУТНЕФТЕГАЗ"</t>
+          <t>АО "АВТОВАЗ"</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8602060555</t>
+          <t>6320002223</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>860201001</t>
+          <t>632001001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ - Югра</t>
+          <t>Самарская область</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://surgutneftegas.ru</t>
+          <t>https://cu-avtovaz.ru</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ОТДЕЛ КАДРОВ</t>
+          <t>учебном центр</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>info@academy-polymer.ru</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>+7 (346) 240-09-07</t>
+          <t>+7 (800) 600-18-31</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://vk.ru/vakansiisurgutneftegasa</t>
+          <t>https://academy-polymer.ru/</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
+          <t>сайт компании</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>ТЕЛ ОТДЕЛ КАДРОВ 8 (3462) 400907, 8 (3462)400913. ... В нефтехимическую лабораторию ПАО "Сургутнефтегаз"требуются лаборанты химического анализа 3,4 разрядов. Вакансии ПАО Сургутнефтегаз</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>ций   г. Нижний Новгород ул. Ульянова, 7   8 (800) 600-18-31   info@academy-polymer.ru   Меню  Главная   Курсы   Конференции   Вебинары   Отзывы   Об учебном центре   Новости   Контакты   Курсы  Базовый   Профили   Бизнес-процессы   Проектирование   Плёнки   Продвинутый   Все курсы →   Будьте в курс</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ПАО "ГАЗ"</t>
+          <t>АО "АВТОВАЗ"</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5200000046</t>
+          <t>6320002223</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>525601001</t>
+          <t>632001001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Нижегородская область</t>
+          <t>Самарская область</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://gaz.ru</t>
+          <t>https://cu-avtovaz.ru</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Вице-президент по персоналу</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Михаленко Дмитрий Геннадьевич</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.tltsu.ru/sveden/struct/obshhestvenno_prosvetitelskii_centr/mixalenko_dmitrii_gennadevic</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>выдача поиска</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>Михаленко Дмитрий Геннадьевич ... Вице-президент по персоналу ОАО «АВТОВАЗ» с 2009 г. Выпускник ТПИ 1995 г. (инженер-электромеханик). Родился 3 июня 1973 г. в... Михаленко Дмитрий Геннадьевич</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1019,41 +1089,42 @@
           <t>https://cu-avtovaz.ru</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>учебном центр</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>info@academy-polymer.ru</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>+7 (800) 600-18-31</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>начальник управления по персоналу</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Кулаков Сергей Николаевич</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://academy-polymer.ru/</t>
+          <t>https://oar-info.ru/sostavsoveta</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>выдача поиска</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>ций   г. Нижний Новгород ул. Ульянова, 7   8 (800) 600-18-31   info@academy-polymer.ru   Меню  Главная   Курсы   Конференции   Вебинары   Отзывы   Об учебном центре   Новости   Контакты   Курсы  Базовый   Профили   Бизнес-процессы   Проектирование   Плёнки   Продвинутый   Все курсы →   Будьте в курс</t>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>Член Совета, Кулаков Сергей Николаевич, Заместитель директора ДпРПП - начальник управления по персоналу АО "АВТОВАЗ" ; Член Совета, Романенко Алексей Николаевич... Состав Совета по профессиональным квалификациям в ...</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1182,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Отключены 
   Закрыть 
@@ -1177,7 +1253,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Андреевский Сергей Иванович - директор, Центр подготовки кадров АК "АЛРОСА" (ПАО), г. ... Контакты: +7 (812) 296-20-50 · +7 (812) 595-02-18. директор, Центр подготовки кадров АК "АЛРОСА" (ПАО), г ...</t>
         </is>
@@ -1241,7 +1322,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>... АК АЛРОСА (ПАО) – «День карьеры АЛРОСА». Мероприятие проводили: Карманова Юлия Сергеевна - заместитель начальника Центра подготовки кадров АК «АЛРОСА... День карьеры АЛРОСА» в Центре алмазных ...</t>
         </is>
@@ -1305,7 +1391,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Управление материально-технического снабжения АК "Алроса" (ПАО) ; Начальник отдела кадров. Теплюкова Ольга Анатольевна ; ИНН / КПП. 1433000147 / 143301001 ; Адрес... Управление материально-технического снабжения АК " ...</t>
         </is>
@@ -1369,7 +1460,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Контакты: Тел: +7 (3952) 40-52-43. Е-mail: lazarevaov@ex.istu.edu. Корпоративно-учебный центр АК АЛРОСА (ПАО) представляет собой современную техническую базу... Корпоративно-учебный центр АК АЛРОСА (ПАО)</t>
         </is>
@@ -1401,12 +1497,12 @@
           <t>https://alrosa.aero</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>службы управления персоналом</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>начальник службы управления персоналом</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Коленченко Евгений Валерьевич</t>
@@ -1421,7 +1517,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>страница руководства</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1429,9 +1525,14 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>Котельникова Ирина Григорьевна  Заместитель директора по экономическим вопросам  Аксаментова Елена Александровна  Заместитель директора - начальник службы управления персоналом  Коленченко Евгений Валерьевич  Заместитель директора по общим и социальным вопросам  Бабушкина Алена Леонидовна  Заместите</t>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>Заместитель директора - начальник службы управления персоналом Коленченко Евгений Валерьевич</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1590,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Руководство. Генеральный директор АО «Авиакомпания АЛРОСА» - руководитель авиационного учебного центра: Хороших Игорь Сергеевич Контактный телефон: +7 (41136)... Авиационный учебный центр</t>
         </is>
@@ -1549,7 +1655,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Корпоративный университет компании «АЛРОСА» - лидера горнодобывающей отрасли. Наша почта CPK@alrosa.ru. Корп университет АЛРОСА (@alrosa_cpk)</t>
         </is>
@@ -1558,45 +1669,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>АК "АЛРОСА" (ПАО)</t>
+          <t>ООО "ЛУКОЙЛ-ЗАПАДНАЯ СИБИРЬ"</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1433000147</t>
+          <t>8608048498</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>143301001</t>
+          <t>860801001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Республика Саха (Якутия)</t>
+          <t>Ханты-Мансийский автономный округ - Югра</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://alrosa.aero</t>
+          <t>https://lukoil.ru</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Центр подготовки кадров АК</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+          <t>Корпоративного университет</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>начальник управления оценки и развития персонала</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Кузьмин Вадим Викторович</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>+7 (812) 595-02-18</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://mmk-international.ru/otzyvy-kliyentov-1/article_post/andreyevskiy-sergey-ivanovich-direktor-tsentr-podgotovki-kadrov-ak-alrosa-pao-g-mirnyy</t>
+          <t>https://www.angi.ru/event/83/</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1609,69 +1724,83 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>ндреевский Сергей Иванович - директор, Центр подготовки кадров АК "АЛРОСА" (ПАО), г. ... Контакты: +7 (812) 296-20-50 · +7 (812) 595-02-18. директор, Центр подготовки кадров АК "АЛРОСА" (ПАО), г ...</t>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>Кузьмин Вадим Викторович, начальник управления оценки и развития персонала ООО "ЛУКОЙЛ-Западная Сибирь". ... Корпоративного университета ООО... Конференция "Повышение качества подготовки кадров как ...</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>АК "АЛРОСА" (ПАО)</t>
+          <t>ООО "ЛУКОЙЛ-ЗАПАДНАЯ СИБИРЬ"</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1433000147</t>
+          <t>8608048498</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>143301001</t>
+          <t>860801001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Республика Саха (Якутия)</t>
+          <t>Ханты-Мансийский автономный округ - Югра</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://alrosa.aero</t>
+          <t>https://lukoil.ru</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>службе управления персоналом</t>
+          <t>Управление развития продаж специальных нефтепродуктов</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Petr.Kaluzhnikov@lukoil.com</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>+7 (914) 113-06-02</t>
+          <t>+7 (495) 981-78-20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://almaz-media.tv/print:page,1,15077-vakansii-alrosa.html</t>
+          <t>https://lukoil.ru/Company/contacts</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
+          <t>сайт компании</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>геофизики. Подробности по тел. +7 914 113-06-02 и в службе управления персоналом (ул. Ленина 44 Б) В АЛРОСА-... ВАКАНСИИ АЛРОСА</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ься  Управление продаж продуктов нефтехимии и газопереработки​  LPGsales@lukoil.com   +7 (495) 981-78-20  По вопросам приобретения кокса обращаться  ​Управление развития продаж специальных нефтепродуктов​  Petr.Kaluzhnikov@lukoil.com   +74999737095   ПРЕСС-СЛУЖБА  Россия, 101000, Москва, Сретенский </t>
         </is>
       </c>
     </row>
@@ -1701,95 +1830,92 @@
           <t>https://lukoil.ru</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Корпоративного университет</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>начальник управления оценки и развития персонала</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Кузьмин Вадим Викторович</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>начальник Управления организации обработки персональных</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>personal.data@lukoil.com</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.angi.ru/event/83/</t>
+          <t>https://lukoil.ru/Company/LegalInformation/PersonalDataProcessingPolicy</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
+          <t>сайт компании</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>Кузьмин Вадим Викторович, начальник управления оценки и развития персонала ООО "ЛУКОЙЛ-Западная Сибирь". ... Корпоративного университета ООО... Конференция "Повышение качества подготовки кадров как ...</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ющих обработку персональных данных, № 08-0009299 ( pd.rkn.gov.ru ).  1.6. Ответственный за организацию обработки персональных данных в ПАО «ЛУКОЙЛ» - начальник Управления организации обработки персональных данных, e-mail&amp;#58; personal.data@lukoil.com .  2. Термины и определения   Для целей Политики </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ООО "ЛУКОЙЛ-ЗАПАДНАЯ СИБИРЬ"</t>
+          <t>ПАО "НЛМК"</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8608048498</t>
+          <t>4823006703</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>860801001</t>
+          <t>482301001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ - Югра</t>
+          <t>Липецкая область</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://lukoil.ru</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Управление развития продаж специальных нефтепродуктов</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Petr.Kaluzhnikov@lukoil.com</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>+7 (495) 981-78-20</t>
-        </is>
-      </c>
+          <t>https://nlmk.com</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Начальник управления по обучению и развитию персонала</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Чикурова Анна Ивановна</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://lukoil.ru/Company/contacts</t>
+          <t>https://lipetsk.nlmk.com/ru/career/corporate-education/management/</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>выдача поиска</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1797,59 +1923,64 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ься  Управление продаж продуктов нефтехимии и газопереработки​  LPGsales@lukoil.com   +7 (495) 981-78-20  По вопросам приобретения кокса обращаться  ​Управление развития продаж специальных нефтепродуктов​  Petr.Kaluzhnikov@lukoil.com   +74999737095   ПРЕСС-СЛУЖБА  Россия, 101000, Москва, Сретенский </t>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Чикурова Анна Ивановна. Начальник управления по обучению и развитию персонала ПАО «НЛМК». Образование: высшее, экономист. Окончила Липецкий Государственный... Руководство образовательной организации НЛМК Липецк</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ООО "ЛУКОЙЛ-ЗАПАДНАЯ СИБИРЬ"</t>
+          <t>ПАО "НЛМК"</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8608048498</t>
+          <t>4823006703</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>860801001</t>
+          <t>482301001</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ - Югра</t>
+          <t>Липецкая область</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://lukoil.ru</t>
+          <t>https://nlmk.com</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>начальник Управления организации обработки персональных</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>personal.data@lukoil.com</t>
-        </is>
-      </c>
+          <t>Директор по персоналу</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Аверченкова Татьяна Михайловна</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://lukoil.ru/Company/LegalInformation/PersonalDataProcessingPolicy</t>
+          <t>https://lipetsk.nlmk.com/ru/career/corporate-education/structure/</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>выдача поиска</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1857,9 +1988,14 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ющих обработку персональных данных, № 08-0009299 ( pd.rkn.gov.ru ).  1.6. Ответственный за организацию обработки персональных данных в ПАО «ЛУКОЙЛ» - начальник Управления организации обработки персональных данных, e-mail&amp;#58; personal.data@lukoil.com .  2. Термины и определения   Для целей Политики </t>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Управляющий директор ПАО «НЛМК» Аверченкова Татьяна Михайловна ; Директор по персоналу ПАО «НЛМК» Коростелёва Ольга Евгеньевна ; Начальник Управления по обучению... Структура и органы управления образовательной ...</t>
         </is>
       </c>
     </row>
@@ -1917,7 +2053,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>podbor@nlmk.com - рабочие профессии podbor@nlmk.com - руководители и специалисты. Люберцы. ООО «Вторчермет НЛМК Центр». Контакты службы по персоналу НЛМК</t>
         </is>
@@ -1950,18 +2091,43 @@
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>начальника отдела мотивации персонала</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Зотову Ю. В.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://disclosure.1prime.ru/Portal/GetDocument.aspx?emId=6623029538&amp;docId=dcfec2bc948242d5a76608fd47c91b28</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>выдача поиска</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>... Научно-производственная корпорация «Уралвагонзавод» Зотову Ю.В. – начальника отдела мотивации персонала ОАО «Научно-производственная корпорация «Уралвагонзавод»... титульный лист</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1989,22 +2155,22 @@
           <t>https://evraz.com</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>учебных центр</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Заместитель директора по персоналу</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Еремеева Ирина Львовна</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>+7 (800) 222-72-00</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.evraz.com/ru/careers/</t>
+          <t>https://social.evraz.com/grant/ekspertnyij-sovet/ural/eremeeva-irina-lvovna.html</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2017,58 +2183,59 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>Обучаем профильным специальностям с нуля в собственных учебных центрах ... Евраз ЗСМК. г. Новокузнецк, пл. Побед, д. 1. +7 (800) 222-72-00 · cpp.zsmk@evraz... Карьера</t>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Заместитель директора по персоналу и социальным вопросам дивизиона «Урал ... Директор по транспорту и логистике АО "ЕВРАЗ ЗСМК". Еремеева Ирина Львовна / Урал / Экспертный совет ...</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>АО "ПО "СЕВМАШ"</t>
+          <t>АО "ЕВРАЗ ЗСМК"</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2902059091</t>
+          <t>4218000951</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>290201001</t>
+          <t>421801001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Архангельская область</t>
+          <t>Кемеровская область</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://sevmash.ru</t>
+          <t>https://evraz.com</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>отдела кадров</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>начальника управления кадров</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Константинова Анна Евгеньевна</t>
-        </is>
-      </c>
+          <t>учебных центр</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>+7 (800) 222-72-00</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://korp29.dvinaland.ru/news/?ELEMENT_ID=200</t>
+          <t>https://www.evraz.com/ru/careers/</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2078,12 +2245,17 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>заместитель начальника управления кадров АО "ПО "Севмаш" Константинова Анна Евгеньевна; начальник отдела кадров АО "ЦС "Звездочка... Корпоративный университет ПАО</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Обучаем профильным специальностям с нуля в собственных учебных центрах ... Евраз ЗСМК. г. Новокузнецк, пл. Побед, д. 1. +7 (800) 222-72-00 · cpp.zsmk@evraz... Карьера</t>
         </is>
       </c>
     </row>
@@ -2113,22 +2285,26 @@
           <t>https://sevmash.ru</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>отдела кадров</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>начальника отдела технического обучения</t>
+          <t>начальника управления кадров</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Красинская Ольга Валериановна</t>
+          <t>Константинова Анна Евгеньевна</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://spk-simt.ru/about-advice/working-groups-spk-simt/rabochaya-gruppa-po-professionalnym-standartam/</t>
+          <t>https://korp29.dvinaland.ru/news/?ELEMENT_ID=200</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2141,9 +2317,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>10. Красинская Ольга Валериановна, заместитель начальника отдела технического обучения, АО «ПО «Севмаш», Северодвинск. 11. Малов Василий Иванович, начальник... Рабочая группа по профессиональным стандартам</t>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>заместитель начальника управления кадров АО "ПО "Севмаш" Константинова Анна Евгеньевна; начальник отдела кадров АО "ЦС "Звездочка... Корпоративный университет ПАО</t>
         </is>
       </c>
     </row>
@@ -2176,19 +2357,19 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>начальник Отдела технического обучения</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>начальника отдела технического обучения</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Красинская Ольга Валериановна</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>+7 (818) 450-51-53</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://shipolymp.narfu.ru/media/documents/111.pdf</t>
+          <t>https://spk-simt.ru/about-advice/working-groups-spk-simt/rabochaya-gruppa-po-professionalnym-standartam/</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2201,9 +2382,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>кадров, тел. +7(818)450-51-53, https://vk.com/ship_olymp. Председатель Оргкомитета, начальник Отдела технического обучения АО «ПО «Севмаш». Заместитель... ОБЛАСТЬ - Всероссийская олимпиада по судостроению</t>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10. Красинская Ольга Валериановна, заместитель начальника отдела технического обучения, АО «ПО «Севмаш», Северодвинск. 11. Малов Василий Иванович, начальник... Рабочая группа по профессиональным стандартам</t>
         </is>
       </c>
     </row>
@@ -2233,22 +2419,22 @@
           <t>https://sevmash.ru</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Учебный центр</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Заместитель генерального директора по управлению персоналом</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Моногаров А. Ю.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>+7 (911) 565-66-89</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://severodvinsk.spravmer.ru/sevmash-otdel-tehnicheskogo-obucheniya-severodvinsk/</t>
+          <t>https://sevmash.ru/download/predlogeniya_celevoi_dogovor.pdf</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2258,57 +2444,62 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>Телефоны: +7 (911) 565-66-89. Подробнее · Учебный центр АО по Севмаш. Учебный центр . Архангельское шоссе, 39, Северодвинск, Архангельская область. Подробнее... Севмаш Отдел технического обучения</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Заместитель генерального директора по управлению персоналом. А.Ю. Моногаров. Page 2. Предложения АО «ПО «Севмаш» размещены на Государственном Портале Работа... размещены - на сайтах: https://sevmash.ru, https://narfu.ru</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ПАО "СЕВЕРСТАЛЬ"</t>
+          <t>АО "ПО "СЕВМАШ"</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3528000597</t>
+          <t>2902059091</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>352801001</t>
+          <t>290201001</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Вологодская область</t>
+          <t>Архангельская область</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://severstal-avia.ru</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Корпоративный университет</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>https://sevmash.ru</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Начальник Отдела технического обучения</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Афанасьев Д. В.</t>
+          <t>Фалев Павел Геннадьевич</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.cfin.ru/management/practice/alt2003-2/02.shtml</t>
+          <t>https://soyuzmash.ru/regional-offices/arkhangelskoe-regionalnoe-otdelenie/</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2321,98 +2512,124 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Корпоративный университет "Северсталь" как инструмент развития бизнеса. Афанасьев Д.В.Корпоративный университет "Северсталь" (Череповец). Поделиться в соц... Корпоративный университет 'Северсталь' как ...</t>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>Фалев Павел Геннадьевич, Начальник Отдела технического обучения АО «ПО «Севмаш» ... 11. Корзин Михаил Геннадьевич, Начальник Управления кадров АО «ПО «Севмаш»... Архангельское</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ПАО "ММК"</t>
+          <t>АО "ПО "СЕВМАШ"</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7414003633</t>
+          <t>2902059091</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>745501001</t>
+          <t>290201001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Челябинская область</t>
+          <t>Архангельская область</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://mmk.ru</t>
+          <t>https://sevmash.ru</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>начальник управления кадров</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Корзин Михаил Геннадьевич</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://spk-simt.ru/about-advice/working-groups-spk-simt/rabochaya-gruppa-po-monitoringu-rynka-truda-i-po-razrabotke-otraslevoy-ramki-kvalifikatsii/</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>не найдено</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>выдача поиска</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>7. Корзин Михаил Геннадьевич. начальник управления кадров. АО «ПО «Севмаш». Северодвинск. 8. Коротков Сергей Владимирович. Рабочая группа по мониторингу рынка труда и ... - СПК ОСК</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ПАО "КАМАЗ"</t>
+          <t>АО "ПО "СЕВМАШ"</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1650032058</t>
+          <t>2902059091</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>165001001</t>
+          <t>290201001</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Республика Татарстан (Татарстан)</t>
+          <t>Архангельская область</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://kamaz.ru</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Корпоративного университет</t>
-        </is>
-      </c>
+          <t>https://sevmash.ru</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>директор Корпоративного университета</t>
+          <t>Заместитель генерального директора по управлению персоналом</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Лейба Светлана Игоревна</t>
+          <t>Моногаров Андрей Юрьевич</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://chelny.kai.ru/main?p_p_id=101&amp;p_p_lifecycle=0&amp;p_p_state=maximized&amp;p_p_mode=view&amp;_101_struts_action=%2Fasset_publisher%2Fview_content&amp;_101_assetEntryId=10868085&amp;_101_type=content&amp;_101_urlTitle=-inovacii-i-tradicii-v-sovremennom-skol-nom-obrazovanii-teoria-i-praktika-</t>
+          <t>https://nok-nark.ru/spk/detail/013</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2425,135 +2642,126 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>От лица ПАО «КАМАЗ» была директор Корпоративного университета Лейба Светлана Игоревна, она отметила о важности и актуальности в наше время ранней профориентации... Образование - Набережночелнинский филиал</t>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>Моногаров Андрей Юрьевич. Заместитель генерального директора по управлению персоналом АО «ПО «Севмаш». Член Совета. Никулина Наталья Викторовна. Директор... СПК в отрасли судостроения и морской техники</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ПАО "КАМАЗ"</t>
+          <t>ПАО "СЕВЕРСТАЛЬ"</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1650032058</t>
+          <t>3528000597</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>165001001</t>
+          <t>352801001</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Республика Татарстан (Татарстан)</t>
+          <t>Вологодская область</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://kamaz.ru</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>учебный центр</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>https://severstal-avia.ru</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Менеджером по персоналу</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>stratonova@kamaz.ru</t>
+          <t>kadri@severstal-avia.com</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>+7 (855) 255-14-62</t>
+          <t>+7 (782) 026-75-21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://ru.linkedin.com/in/анатолий-рыженков-697265105</t>
+          <t>https://severstal-avia.ru/severstal-avia/vakansii/</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
+          <t>страница руководства</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>Начальник учебно-методического отдела, stratonova@kamaz.ru, 8 (8552) 55-14-62 ... (c) 2023 ЧОУ ДПО «МИТТУ». Корпоративный учебный центр ПАО КАМАЗ. Сервис... Руководство</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>График работы:  сменный  Зарплата:  от 100000₽  Смотреть вакансию   По вопросам доступных вакансий и работы в Северсталь Авиа можно связаться с нашим Менеджером по персоналу kadri@severstal-avia.com, +7 (8202) 675-218.  ООО «Авиапредприятие «Северсталь» использует файлы «cookie» с целью персонализац</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ПАО "КАМАЗ"</t>
+          <t>ПАО "ММК"</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1650032058</t>
+          <t>7414003633</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>165001001</t>
+          <t>745501001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Республика Татарстан (Татарстан)</t>
+          <t>Челябинская область</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://kamaz.ru</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>учебного центр</t>
-        </is>
-      </c>
+          <t>https://mmk.ru</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>office@korib.ru</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>https://korib.ru/uc-news</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>зинговая компания «КАМАЗ» · ООО «АвтоЗапчасть КАМАЗ» · Запчасти на КАМАЗ · Проложить маршрут Карта партнера office@korib.ru... дилера КАМАЗ - Новости учебного центра</t>
-        </is>
-      </c>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2583,25 +2791,33 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>учебный центр</t>
+          <t>Учебно-методическим центром</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Самаркина Ольга Викторовна</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SamarkinaOV@kamaz.ru</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>+7 (800) 555-00-99</t>
+          <t>+7 (855) 237-45-54</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://kamaz.ru/career/sotrudnikam/education/</t>
+          <t>https://profkamaz.ru/contact/</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>страница руководства</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2609,9 +2825,14 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>Корпоративный учебный центр   --&gt;  Call-центр с 6:00 - 22:00 МСК   8 (800) 555-00-99   Войти   Зарегистрироваться   --&gt;  Хочу работать на «КАМАЗЕ»   ru   en   О компании   О компании   Общая информация   История   Сведения о регистрации и товарном знаке   Достижения и награды   Политики   Устойчивое</t>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>ена Александровна Бухгалтер-кассир   (8552) 37-45-48   Грунина Татьяна Евгеньевна Бухгалтер   (8552) 37-45-51   Самаркина Ольга Викторовна Заведующая Учебно-методическим центром   (8552) 37-45-54   SamarkinaOV@kamaz.ru   Касымова Лидия Александровна Начальник отдела по работе с молодежью   (8552) 45</t>
         </is>
       </c>
     </row>
@@ -2643,20 +2864,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>учебном центр</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+          <t>Корпоративного университет</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>директор Корпоративного университета</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Лейба Светлана Игоревна</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>+7 (855) 292-89-52</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://mcpkm.ru/ob-mcpk/obschaja-informacija/</t>
+          <t>https://chelny.kai.ru/main?p_p_id=101&amp;p_p_lifecycle=0&amp;p_p_state=maximized&amp;p_p_mode=view&amp;_101_struts_action=%2Fasset_publisher%2Fview_content&amp;_101_assetEntryId=10868085&amp;_101_type=content&amp;_101_urlTitle=-inovacii-i-tradicii-v-sovremennom-skol-nom-obrazovanii-teoria-i-praktika-</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2669,9 +2894,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>алификации работников ПАО «КАМАЗ» и обучение персонала новым профессиям. ... Телефоны. 8 (8552) 92-89-52 тел/факс; 8 (8552) 92... Общая информация об учебном центре ...</t>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>От лица ПАО «КАМАЗ» была директор Корпоративного университета Лейба Светлана Игоревна, она отметила о важности и актуальности в наше время ранней профориентации... Образование - Набережночелнинский филиал</t>
         </is>
       </c>
     </row>
@@ -2703,88 +2933,89 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Учебный центр</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>управлению персоналом</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>генерального директора по управлению персоналом</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Толмачева Галина Алексеевна</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>+7 (812) 385-10-32</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://deklarantonline.ru/5-8-dekabrya-uc-kompas-ved-provel-obuchenie-dlya-sotrudnikov-pao-kamaz-v-g-naberezhnye-chelny/</t>
+          <t>https://profkamaz.ru/contact/</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
+          <t>страница руководства</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>учение специалистов отдела закупок запасных частей ПАО «КАМАЗ». ... перезвоните по телефону: +7 (812) 385-10-32 для подтверждения... С 5 по 8 декабря Учебный центр «Компас ВЭД» провел ...</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Приемные дни ср., пт. 15:00 - 17:00  Место нахождения Исполнительная дирекция, 3 этаж, каб. 303  Первичная профсоюзная организация Блока заместителя генерального директора по управлению персоналом, организационному развитию и корпоративному управлению и Центра правового обеспечения  ФИО  Должность  </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ПАО "ОДК-САТУРН"</t>
+          <t>ПАО "КАМАЗ"</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7610052644</t>
+          <t>1650032058</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>761001001</t>
+          <t>165001001</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ярославская область</t>
+          <t>Республика Татарстан (Татарстан)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://yartpp.ru</t>
+          <t>https://kamaz.ru</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>отдела кадров</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>начальник отдела кадров</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Рыжакова Александра Юрьевна</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>+7 (961) 155-39-39</t>
-        </is>
-      </c>
+          <t>учебного центр</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>office@korib.ru</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://nnt.ugrasu.ru/upload/files/vakansii/Потребность в сотрудниках ОДК-Сатурн.pdf</t>
+          <t>https://korib.ru/uc-news</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2797,73 +3028,79 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>Представитель работодателя: начальник отдела кадров ПАО «ОДК-Сатурн». Рыжакова Александра Юрьевна, тел. 8-961-155-39-39. Заработная плата... Потребность в сотрудниках ПАО "ОДК-Сатурн"</t>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>зинговая компания «КАМАЗ» · ООО «АвтоЗапчасть КАМАЗ» · Запчасти на КАМАЗ · Проложить маршрут Карта партнера office@korib.ru... дилера КАМАЗ - Новости учебного центра</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ПАО "ОДК-САТУРН"</t>
+          <t>ПАО "КАМАЗ"</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7610052644</t>
+          <t>1650032058</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>761001001</t>
+          <t>165001001</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ярославская область</t>
+          <t>Республика Татарстан (Татарстан)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://yartpp.ru</t>
+          <t>https://kamaz.ru</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>отдела кадров</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Начальник отдела кадров</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Воронецкая Татьяна Сергеевна</t>
-        </is>
-      </c>
+          <t>учебный центр</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>+7 (800) 555-00-99</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://trud.yarregion.ru/employer/detail/?companyId=ec13956c-08d1-11e2-bbf7-005056876601</t>
+          <t>https://kamaz.ru/career/sotrudnikam/education/</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>выдача поиска</t>
+          <t>сайт компании</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>Публичное акционерное общество "ОДК-Сатурн" · Начальник отдела кадров. Воронецкая Татьяна Сергеевна · ИНН / КПП. 7610052644 / 761001001 · Адрес электронной почты. Публичное акционерное общество "ОДК-Сатурн"</t>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>Корпоративный учебный центр   --&gt;  Call-центр с 6:00 - 22:00 МСК   8 (800) 555-00-99   Войти   Зарегистрироваться   --&gt;  Хочу работать на «КАМАЗЕ»   ru   en   О компании   О компании   Общая информация   История   Сведения о регистрации и товарном знаке   Достижения и награды   Политики   Устойчивое</t>
         </is>
       </c>
     </row>
@@ -2895,24 +3132,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Учебного центр</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>saturn@uec-saturn.ru</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>+7 (748) 553-28-10</t>
-        </is>
-      </c>
+          <t>отдела кадров</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Начальник отдела кадров</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Воронецкая Татьяна Сергеевна</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.uecrus.com/about/structure/pao-odk-saturn/kontakty-cok-saturn/</t>
+          <t>https://trud.yarregion.ru/employer/detail/?companyId=ec13956c-08d1-11e2-bbf7-005056876601</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2925,9 +3162,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>... Контакты. +7 (4855) 328-100 saturn@uec-saturn.ru. Контакты. Центр оценки квалификации расположен на территории Учебного центра ПАО «ОДК-Сатурн» по адресу: Контакты - ПАО «ОДК-Сатурн»</t>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "ОДК-Сатурн" · Начальник отдела кадров. Воронецкая Татьяна Сергеевна · ИНН / КПП. 7610052644 / 761001001 · Адрес электронной почты. Публичное акционерное общество "ОДК-Сатурн"</t>
         </is>
       </c>
     </row>
@@ -2959,24 +3201,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Отдел кадров</t>
+          <t>Учебного центр</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>personal@uec-saturn.ru</t>
+          <t>saturn@uec-saturn.ru</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>+7 (748) 553-28-31</t>
+          <t>+7 (748) 553-28-10</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://mintrudri.ru/news2/3250-rabochie-mesta-v-kampanii-odk-saturn</t>
+          <t>https://www.uecrus.com/about/structure/pao-odk-saturn/kontakty-cok-saturn/</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2989,9 +3231,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>... адрес: personal@uec-saturn.ru. Контакты Отдел кадров ПАО «ОДК-Сатурн» г. Рыбинск, пр. Ленина, 163, кабинет 113 Тел.: +7 (4855) 328-318, +7... Рабочие места в кампании "ОДК Сатурн"</t>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>... Контакты. +7 (4855) 328-100 saturn@uec-saturn.ru. Контакты. Центр оценки квалификации расположен на территории Учебного центра ПАО «ОДК-Сатурн» по адресу: Контакты - ПАО «ОДК-Сатурн»</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3280,8 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3093,7 +3341,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Режим работы: Пн-Пт: 07:45 — 17:00 · Цыгина Ольга Дмитриевна руководитель Корпоративного университета ПАО «Татнефть» · Цыплёнок Алексей Сергеевич · Глазкова Ольга... Контакты - Корпоративный университет - ПАО «Татнефть</t>
         </is>
@@ -3157,7 +3410,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>— 17:00 · Цыгина Ольга Дмитриевна руководитель Корпоративного университета ПАО «Татнефть» · Цыплёнок Алексей Сергеевич · Глазкова Ольга... Контакты - Корпоративный университет - ПАО «Татнефть</t>
         </is>
@@ -3189,22 +3447,22 @@
           <t>https://tatneft.ru</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Отдел развития иноязычной компетенции и</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Начальник управления по работе с персоналом</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Бочкарева Светлана Анатольевна</t>
+          <t>Глазков Андрей Александрович</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/bochkareva-svetlana-anatolevna?lang=ru</t>
+          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/glazkov-andrey-aleksandrovich</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3217,9 +3475,14 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>Начальник отдела, Отдел развития иноязычной компетенции и анализа ... ПАО "Татнефть" им. В.Д. Шашина, Обучение по дополнительной профессиональной... Татнефть» - Бочкарева Светлана Анатольевна</t>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Глазков Андрей Александрович ... Начальник управления по работе с персоналом ПАО "Татнефть". Общий стаж работы: 13 лет. Стаж в сфере образования: 13 лет. Ученая... Татнефть» - Глазков Андрей Александрович</t>
         </is>
       </c>
     </row>
@@ -3249,22 +3512,22 @@
           <t>https://tatneft.ru</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Корпоративный университет</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Начальник управления по работе с персоналом</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Сафиуллина Инесса Геннадьевна</t>
+          <t>Шашина В. Д.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/safiullina-inessa-gennadevna?lang=ru</t>
+          <t>http://komitet-energo.duma.gov.ru/about/ekspertnyj-sovet/sekcii-ekspertnogo-soveta/51c2c9ed-7edc-4900-b341-c79b79007f15</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3274,12 +3537,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Сафиуллина Инесса Геннадьевна ... Руководитель группы, Группа сопровождения и реализации индивидуальных планов развития, Корпоративный университет ПАО «Татнефть»,... Татнефть» - Сафиуллина Инесса Геннадьевна</t>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>6. ГЛАЗКОВ Андрей Александрович. Начальник управления по работе с персоналом ПАО «Татнефть» им.В.Д.Шашина» ; 7. ГУБКИН Анатолий Алексеевич. Руководитель... Секция по законодательному регулированию социальной ...</t>
         </is>
       </c>
     </row>
@@ -3311,20 +3579,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Корпоративный университет</t>
+          <t>Отдел развития иноязычной компетенции и</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Патрикеев Александр Андреевич</t>
+          <t>Бочкарева Светлана Анатольевна</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/patrikeev-aleksandr-andreevich?lang=ru</t>
+          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/bochkareva-svetlana-anatolevna?lang=ru</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3337,75 +3605,215 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>Патрикеев Александр Андреевич ... Заместитель начальника, Отдел инновационных технологий и обучения, Корпоративный университет ПАО «Татнефть», Центр обслуживания... Татнефть» - Патрикеев Александр Андреевич</t>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>Начальник отдела, Отдел развития иноязычной компетенции и анализа ... ПАО "Татнефть" им. В.Д. Шашина, Обучение по дополнительной профессиональной... Татнефть» - Бочкарева Светлана Анатольевна</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
+          <t>ПАО "ТАТНЕФТЬ" ИМ. В.Д. ШАШИНА</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4205049090</t>
+          <t>1644003838</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>420501001</t>
+          <t>164401001</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Кемеровская область</t>
+          <t>Республика Татарстан (Татарстан)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://kru.ru</t>
+          <t>https://tatneft.ru</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Учебного центр</t>
+          <t>Корпоративный университет</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
+          <t>Сафиуллина Инесса Геннадьевна</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/safiullina-inessa-gennadevna?lang=ru</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>выдача поиска</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>Сафиуллина Инесса Геннадьевна ... Руководитель группы, Группа сопровождения и реализации индивидуальных планов развития, Корпоративный университет ПАО «Татнефть»,... Татнефть» - Сафиуллина Инесса Геннадьевна</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ПАО "ТАТНЕФТЬ" ИМ. В.Д. ШАШИНА</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1644003838</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>164401001</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Республика Татарстан (Татарстан)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://tatneft.ru</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Корпоративный университет</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Патрикеев Александр Андреевич</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://cu.tatneft.ru/ob-universitete/pedagogicheskiy-sostav/patrikeev-aleksandr-andreevich?lang=ru</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>выдача поиска</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>Патрикеев Александр Андреевич ... Заместитель начальника, Отдел инновационных технологий и обучения, Корпоративный университет ПАО «Татнефть», Центр обслуживания... Татнефть» - Патрикеев Александр Андреевич</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4205049090</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>420501001</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Кемеровская область</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://kru.ru</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Учебного центр</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>Соленцова Мария Алексеевна</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>solencova@kru.ru</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>+7 (384) 244-07-40</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">5:55, без перерыва между занятиями внутри пары (перерыв на обед 12:00
   – 13:00).
@@ -3415,69 +3823,74 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Учебного центр</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Деревцова Екатерина Михайловна</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>derevcova@kru.ru</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>+7 (384) 244-02-82</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>мовна  8 (384) 244-02-82 
   kazakova@kru.ru 
@@ -3487,65 +3900,70 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Учебного центр</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Специалисты по подготовке кадров</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Соленцова Мария Алексеевна</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>льной организацией  Учебный центр является структурным подразделением УК «Кузбассразрезуголь».  Соленцова Мария Алексеевна Начальник Учебного центра  Специалисты по подготовке кадров   Казакова Юлия Максимовна 
   Главный специалист 
@@ -3555,65 +3973,70 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Учебный центр</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Ведущий специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Полуянчик Екатерина Витаутасовна</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>й специалист по подготовке кадров 
   Мирошникова Надежда Николаевна 
@@ -3627,65 +4050,70 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Учебный центр</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Ведущий специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Курдюмова Наталья Александровна</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">специалист по подготовке кадров 
   Полуянчик Екатерина Витаутасовна 
@@ -3700,65 +4128,70 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Учебный центр</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Кирсанова Елена Олеговна</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Ведущий специалист по подготовке кадров 
   Курдюмова Наталья Александровна 
@@ -3771,65 +4204,70 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Учебный центр</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>Прошин Андрей Владимирович</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>ова Елена Олеговна 
   Специалист по подготовке кадров 
@@ -3839,61 +4277,66 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
         <is>
           <t>Главный специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Казаева Татьяна Феоктистовна</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>ке кадров   Казакова Юлия Максимовна 
   Главный специалист 
@@ -3908,61 +4351,66 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>Главный специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Еськова Ольга Вячеславовна</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">катерина Михайловна 
   Ведущий специалист 
@@ -3977,61 +4425,66 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Главный специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>Шурохайлова Наталья Ильинична</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Главный специалист по подготовке кадров 
   Еськова Ольга Вячеславовна 
@@ -4045,61 +4498,66 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
         <is>
           <t>Главный специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Кондратюк Евгения Сергеевна</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Главный специалист по подготовке кадров 
   Шурохайлова Наталья Ильинична 
@@ -4112,61 +4570,66 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
         <is>
           <t>Главный специалист по подготовке кадров</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Мирошникова Надежда Николаевна</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>лавный специалист по подготовке кадров 
   Кондратюк Евгения Сергеевна 
@@ -4179,65 +4642,70 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Учебного центр</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
         <is>
           <t>solencova@kru.ru</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>+7 (384) 244-07-40</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>https://kru.ru/training-center.html</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>solencova@kru.ru 
   +7 (3842) 44-07-40 
@@ -4245,65 +4713,70 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>4205049090</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>420501001</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Кемеровская область</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>Учебный центр</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
         <is>
           <t>office@kru.ru</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>+7 (384) 244-03-00</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>https://kru.ru/contacts.html</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Кузбассразрезуголь 
   Учебный центр 
@@ -4318,126 +4791,6 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>4205049090</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>420501001</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>https://kru.ru</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>директор по персоналу</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>globus-j@mail.ru</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://www.vnedra.ru/glavnaya-tema/kuzbassrazrezugol-60-let-u-istokov-energii-24923/</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>выдача поиска</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>... директор по персоналу и общим вопросам УК «Кузбассразрезуголь» Евгения Бажина. ... e-mail: globus-j@mail.ru · vkontakte · Яндекс Дзен · Telegram · О журнале... Кузбассразрезуголь»: 60 лет у истоков энергии</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>АО "УК "КУЗБАССРАЗРЕЗУГОЛЬ"</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>4205049090</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>420501001</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Кемеровская область</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>https://kru.ru</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>учебный центр</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>+7 (384) 244-01-27</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://foedu.ru/kemerovskaya-oblast/ostalnye-naselennye-punkty/povyshenie-kvalifikacii-i-professionalnaya-perepodgotovka/kuzbassrazrezugol-uchebnyy-centr.html</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>выдача поиска</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>Кузбассразрезуголь, учебный центр ; 652642 Берёзовая, 38, Кемеровская область · +7 (3842) 44-01-27 · +7 (384) 527-29-44 · +7 (384) 527-30-09 · +7 (384) 527-30-44. Кузбассразрезуголь, учебный центр Кемеровская область</t>
-        </is>
-      </c>
-    </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
@@ -4464,22 +4817,22 @@
           <t>https://kru.ru</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>учебный центр</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>директор по персоналу</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>+7 (384) 527-30-44</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>globus-j@mail.ru</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://foedu.ru/kemerovskaya-oblast/ostalnye-naselennye-punkty/povyshenie-kvalifikacii-i-professionalnaya-perepodgotovka/kuzbassrazrezugol-uchebnyy-centr.html</t>
+          <t>https://www.vnedra.ru/glavnaya-tema/kuzbassrazrezugol-60-let-u-istokov-energii-24923/</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4492,9 +4845,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>; 652642 Берёзовая, 38, Кемеровская область · +7 (3842) 44-01-27 · +7 (384) 527-29-44 · +7 (384) 527-30-09 · +7 (384) 527-30-44. Кузбассразрезуголь, учебный центр Кемеровская область</t>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>... директор по персоналу и общим вопросам УК «Кузбассразрезуголь» Евгения Бажина. ... e-mail: globus-j@mail.ru · vkontakte · Яндекс Дзен · Telegram · О журнале... Кузбассразрезуголь»: 60 лет у истоков энергии</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4910,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Бикмурзин Азат Шаукатович – Генеральный директор ПАО «Нижнекамскнефтехим»; ... Шуйский Василий Николаевич — заместитель генерального директора по персоналу и... Гордость института</t>
         </is>
@@ -4616,7 +4979,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>сть Университета.  Начальник: Инюкина Маргарита Васильевна Телефон: +7 (8152) 40-33-56   Учебно-экспериментальный цех   Телефон: +7 (8152) 40-34-38   Учебно-научный центр «Инженерная школа АФ МАУ»   Международный информационно-аналитический центр междисциплинарных исследований развития Арктической з</t>
         </is>
@@ -4625,53 +4993,45 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ПАО "УРАЛКАЛИЙ"</t>
+          <t>АО "КОЛЬСКАЯ ГМК"</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5911029807</t>
+          <t>5191431170</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>591101001</t>
+          <t>510701001</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Пермский край</t>
+          <t>Мурманская область</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://uralkali.com</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>управлению персоналом</t>
-        </is>
-      </c>
+          <t>https://kolagmk.ru</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>директор по персоналу</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>info@permnews.ru</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>+7 (342) 201-77-37</t>
-        </is>
-      </c>
+          <t>директор департамента по персоналу</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Крыгина А. Ю.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://permnews.ru/novosti/economy/2026/07/10/ralkaliy_priznan_liderom_po_upravleniyu_personalom/</t>
+          <t>https://rudmet.net/journal/1911/article/32428/?language=ru</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4684,54 +5044,59 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>Заместитель генерального директора — директор по персоналу и коммуникациям ПАО «Уралкалий ... +7(342) 201-77-37, e-mail: info@permnews.ru... Уралкалий» признан лидером по управлению персоналом</t>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>АО «Кольская ГМК», Мончегорск, Россия: А. Ю. Крыгина, заместитель генерального директора — директор департамента по персоналу и социальной политике,... АО «Кольская ГМК» — о спорте, туризме и творчестве</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ПАО "УРАЛКАЛИЙ"</t>
+          <t>АО "КОЛЬСКАЯ ГМК"</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5911029807</t>
+          <t>5191431170</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>591101001</t>
+          <t>510701001</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Пермский край</t>
+          <t>Мурманская область</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://uralkali.com</t>
+          <t>https://kolagmk.ru</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>директор по персоналу</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>ethics@uralkali.com</t>
-        </is>
-      </c>
+          <t>директор департамента по персоналу</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Ильясов Руслан Маратович</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.uralkali.com/ru/sustainability/ethics/business_ethics/</t>
+          <t>http://sovethr.ru/home/o-sovete-hr/sostav-soveta/</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4741,12 +5106,17 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>Ирина Константинова — заместитель генерального директора — директор по персоналу и коммуникациям ПАО «Уралкалий» ... e-mail: ethics@uralkali.com. Смотрите... Деловая этика | ПАО «Уралкалий»</t>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>Ильясов Руслан Маратович, Заместитель генерального директора-директор департамента по персоналу и соцполитике АО «Кольская ГМК» («ГМК «Норильский никель»). Состав Совета</t>
         </is>
       </c>
     </row>
@@ -4778,20 +5148,28 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Дирекция по персоналу</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>управлению персоналом</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>директор по персоналу</t>
+        </is>
+      </c>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>info@permnews.ru</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>+7 (342) 429-60-53</t>
+          <t>+7 (342) 201-77-37</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.uralkali.com/ru/about/contacts/</t>
+          <t>https://permnews.ru/novosti/economy/2026/07/10/ralkaliy_priznan_liderom_po_upravleniyu_personalom/</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4801,66 +5179,67 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>ПАО «Уралкалий». ул. Пятилетки, 63, Березники Пермский край, Россия, 618426 ... Дирекция по персоналу и коммуникациям. Тел.: +7 (3424) 29 60 53. E-mail... Контакты | ПАО «Уралкалий»</t>
+          <t>сторонний сайт, компания упомянута</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>подтверждено на странице</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>Заместитель генерального директора — директор по персоналу и коммуникациям ПАО «Уралкалий ... +7(342) 201-77-37, e-mail: info@permnews.ru... Уралкалий» признан лидером по управлению персоналом</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ПАО "ЕВРАЗ"</t>
+          <t>ПАО "УРАЛКАЛИЙ"</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6623000680</t>
+          <t>5911029807</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>662301001</t>
+          <t>591101001</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Свердловская область</t>
+          <t>Пермский край</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://evraz.ru</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Учебный центр</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>https://uralkali.com</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>директор по персоналу</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Olga.Egorova2@evraz.com</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>+7 (343) 549-87-43</t>
-        </is>
-      </c>
+          <t>ethics@uralkali.com</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://cpp-evraz-ural.ru/sveden/struct/</t>
+          <t>https://www.uralkali.com/ru/sustainability/ethics/business_ethics/</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>выдача поиска</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -4868,63 +5247,64 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eksej.Makarov@evraz.com   +7 (3435) 49-67-95   622025, Свердловская обл., г. Нижний Тагил, ул. Индустриальная, 70, Корпус 5, 3-й этаж, кабинет №324   Учебный центр  Егорова   Ольга Александровна   Начальник учебного центра   Olga.Egorova2@evraz.com   +7 (3435) 49-87-43   Положение об учебном центре </t>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Ирина Константинова — заместитель генерального директора — директор по персоналу и коммуникациям ПАО «Уралкалий» ... e-mail: ethics@uralkali.com. Смотрите... Деловая этика | ПАО «Уралкалий»</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ПАО "ЕВРАЗ"</t>
+          <t>ПАО "УРАЛКАЛИЙ"</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6623000680</t>
+          <t>5911029807</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>662301001</t>
+          <t>591101001</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Свердловская область</t>
+          <t>Пермский край</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://evraz.ru</t>
+          <t>https://uralkali.com</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Учебный центр</t>
+          <t>Дирекция по персоналу</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Aleksej.Makarov@evraz.com</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
-          <t>+7 (343) 549-67-95</t>
+          <t>+7 (342) 429-60-53</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://cpp-evraz-ural.ru/sveden/manager/</t>
+          <t>https://www.uralkali.com/ru/about/contacts/</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>сайт компании</t>
+          <t>выдача поиска</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -4932,75 +5312,223 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>Mikhail.Kholkin@evraz.com   +7 (3435) 49-72-71   Макаров   Алексей Юрьевич   Заместитель директора   Aleksej.Makarov@evraz.com   +7 (3435) 49-67-95   Учебный центр  Егорова   Ольга Александровна   Начальник учебного центра   Olga.Egorova2@evraz.com   +7 (3435) 49-87-43   Экономический отдел  Сорокин</t>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>ПАО «Уралкалий». ул. Пятилетки, 63, Березники Пермский край, Россия, 618426 ... Дирекция по персоналу и коммуникациям. Тел.: +7 (3424) 29 60 53. E-mail... Контакты | ПАО «Уралкалий»</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>ПАО "ЕВРАЗ"</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6623000680</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>662301001</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Свердловская область</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>https://evraz.ru</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Учебный центр</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Olga.Egorova2@evraz.com</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>+7 (343) 549-87-43</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://cpp-evraz-ural.ru/sveden/struct/</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eksej.Makarov@evraz.com   +7 (3435) 49-67-95   622025, Свердловская обл., г. Нижний Тагил, ул. Индустриальная, 70, Корпус 5, 3-й этаж, кабинет №324   Учебный центр  Егорова   Ольга Александровна   Начальник учебного центра   Olga.Egorova2@evraz.com   +7 (3435) 49-87-43   Положение об учебном центре </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ПАО "ЕВРАЗ"</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>6623000680</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>662301001</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Свердловская область</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://evraz.ru</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Учебный центр</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Aleksej.Makarov@evraz.com</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>+7 (343) 549-67-95</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://cpp-evraz-ural.ru/sveden/manager/</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>Mikhail.Kholkin@evraz.com   +7 (3435) 49-72-71   Макаров   Алексей Юрьевич   Заместитель директора   Aleksej.Makarov@evraz.com   +7 (3435) 49-67-95   Учебный центр  Егорова   Ольга Александровна   Начальник учебного центра   Olga.Egorova2@evraz.com   +7 (3435) 49-87-43   Экономический отдел  Сорокин</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
           <t>АО "УРАЛЬСКАЯ СТАЛЬ"</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>5607019523</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>560701001</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Оренбургская область</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>https://uralsteel.com</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Учебного центр</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
         <is>
           <t>Дыга Евгения Константиновна</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>info@uralsteel.com</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>+7 (353) 766-21-53</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>https://uralsteel.com/career/evolution/</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">359, Оренбургская обл., г. Новотроицк, ул. Советская, д.64
   Руководитель функционального направления : 
@@ -5013,129 +5541,139 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>АО "УРАЛЬСКАЯ СТАЛЬ"</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>5607019523</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>560701001</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Оренбургская область</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>https://uralsteel.com</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>Учебного центр</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Руководитель Учебного центра</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Пухов Дмитрий Валерьевич</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
         <is>
           <t>https://uralsteel.com/upload/Information.pdf</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>выдача поиска</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>АО «Уральская Сталь» выдана Министерством образования по Оренбургской ... Руководитель Учебного центра: Пухов Дмитрий Валерьевич. Режим работы Учебного... Сведения об образовательной организации</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>АО "УРАЛЬСКАЯ СТАЛЬ"</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>5607019523</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>560701001</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Оренбургская область</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>https://uralsteel.com</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Учебный центр</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
         <is>
           <t>info@uralsteel.com</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>+7 (353) 766-21-53</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>https://uralsteel.com/career/evolution/</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">едельник – четверг с 08:00 до 17:00, пятница: с 08:00 до 16:00
   Перерыв : 
@@ -5150,61 +5688,66 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>АО "УРАЛЬСКАЯ СТАЛЬ"</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>5607019523</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>560701001</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Оренбургская область</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>https://uralsteel.com</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Учебного центр</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
         <is>
           <t>Дыга Евгения Константиновна</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
         <is>
           <t>https://uralsteel.com/career/evolution/</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>сайт компании</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>сайт компании</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>нформация  Юридический адрес Общества : 
   462353, Оренбургская обл., г. Новотроицк, ул. Заводская, д.1, АО «Уральская Сталь»
@@ -5215,126 +5758,6 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>АО "УРАЛЬСКАЯ СТАЛЬ"</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>5607019523</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>560701001</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Оренбургская область</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>https://uralsteel.com</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Учебного центр</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Аносова Наталья Георгиевна</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>https://ztz.ru/career/staff-development/</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>выдача поиска</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>Аносова Наталья Георгиевна – начальник Учебного центра. Место ... АО «Уральская Сталь». АО «Уральская Сталь» – промышленный гигант Оренбургской... Развитие персонала - ЗТЗ</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>ПАО "ЯКОВЛЕВ"</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3807002509</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>771401001</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Г.Москва</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>https://yakovlev.ru</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>УЧЕБНЫЙ ЦЕНТР</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Яковлев Дмитрий Дмитриевич</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>https://rating.gd.ru/profile/jakovlev-dmitriy-dmitrievich_9/</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>выдача поиска</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>Яковлев Дмитрий возглавляет компанию НЕГОСУДАРСТВЕННОЕ УЧРЕЖДЕНИЕ ОРГАНИЗАЦИЯ ДОПОЛНИТЕЛЬНОГО ПРОФЕССИОНАЛЬНОГО ОБРАЗОВАНИЯ "УЧЕБНЫЙ ЦЕНТР "АВТО... Рейтинг Яковлев Дмитрий Дмитриевич</t>
-        </is>
-      </c>
-    </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -5361,22 +5784,22 @@
           <t>https://yakovlev.ru</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>отдела подготовки кадров</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>shirenina_ev@iaz.yakovlev.ru</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Начальник управления кадров</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Данилова С. Г.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://prof.iro38.ru/public/storage/files/cnwq6n8JXfKVVZTv29WsLdFWFzNpu7G2OYlg9fME.pdf</t>
+          <t>https://appeal.chuvgpu.ru/?page=33</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5389,9 +5812,14 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N79" s="2" t="inlineStr">
-        <is>
-          <t>руководитель группы отдела подготовки кадров, 8(3952). 45-18-74, shirenina_ev@iaz.yakovlev.ru. 2. Иркутская область. Инженерный дизайн САПР. Филиал ПАО "Яковлев... Ответственный специалист от</t>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>Яковлев ячĕллĕ Чăваш патшалăх педагогика университечĕ. Контактная информация ... Начальник управления кадров и правового обеспечения С.Г. Данилова. #417... Электронная приемная ЧГПУ им. И.Я. Яковлева</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5877,12 @@
           <t>сторонний сайт, компания упомянута</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>страница недоступна, проверить вручную</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Директор департамента управления персоналом ПАО "Яковлев". Бугреев Владимир ... E-mail: prof@uacrussia.ru. Состав совета по профессиональным квалификациям в ...</t>
         </is>
@@ -5517,7 +5950,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>tie/uchebnyy-tsentr/   Руководитель образовательной организации  Ездокова Ульяна Александровна  Директор по обучению и развитию персонала – начальник учебного центра ВСМПО  Электронная почта: Ezdokova_ua@vsmpo-avisma.ru   Телефон: +79676382001  Положение об Учебном центре  PDF   (1.2 мб)   ДОКУМЕНТЫ</t>
         </is>
@@ -5581,7 +6019,12 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>:00. Суббота, воскресенье — выходной день.  +7 (34345) 6-17-25, 6-34-34  [email protected]   Структура и органы управления  Организационная структура учебного центра ВСМПО  Должность   Фамилия Имя Отчество   Адрес электронной почты   Номер телефона   Директор по обучению и развитию персонала - начал</t>
         </is>
@@ -5645,74 +6088,19 @@
           <t>сайт компании</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>со своего сайта</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">обучению и развитию персонала – начальник учебного центра ВСМПО  Электронная почта: Ezdokova_ua@vsmpo-avisma.ru   Телефон: +79676382001  Положение об Учебном центре  PDF   (1.2 мб)   ДОКУМЕНТЫ  Устав ПАО Корпорация ВСМПО-АВИСМА  PDF   (1.3 мб)   Правила внутреннего трудового распорядка  PDF   (28.8 </t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>ПАО "КОРПОРАЦИЯ ВСМПО-АВИСМА"</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>6607000556</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>662301001</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Свердловская область</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>https://vsmpo.ru</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>управлению персоналом</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>+7 (343) 456-17-03</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>https://info-torg.ru/kartochka-kompanii/?fid=4388&amp;amp;cid=34345&amp;amp;type=contacts&amp;amp;adr_id=2</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>выдача поиска</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>сторонний сайт, компания упомянута</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>Контакты · ВСМПО-АВИСМА дирекция по управлению персоналом (ПАО Корпорация "ВСМПО-АВИСМА") · Телефоны: +7 (34345) 6-17-03 отдел подбора песонала · Время работы:. ВСМПО-АВИСМА дирекция по управлению персоналом</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N84"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>